--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486718_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486718_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>12.1801</v>
+        <v>12.6268</v>
       </c>
       <c r="E2" t="n">
-        <v>9.911199999999999</v>
+        <v>10.5318</v>
       </c>
       <c r="F2" t="n">
-        <v>2.2689</v>
+        <v>2.0951</v>
       </c>
       <c r="G2" t="n">
         <v>8.5047</v>
@@ -610,13 +610,13 @@
         <v>3.6685</v>
       </c>
       <c r="S2" t="n">
-        <v>0.2706</v>
+        <v>0.7173</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.6071</v>
+        <v>0.0134</v>
       </c>
       <c r="U2" t="n">
-        <v>0.8778</v>
+        <v>0.7039</v>
       </c>
       <c r="V2" t="n">
         <v>3.5978</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>6.8636</v>
+        <v>6.0154</v>
       </c>
       <c r="E3" t="n">
-        <v>4.2165</v>
+        <v>3.4926</v>
       </c>
       <c r="F3" t="n">
-        <v>2.647</v>
+        <v>2.5229</v>
       </c>
       <c r="G3" t="n">
         <v>1.7674</v>
@@ -688,13 +688,13 @@
         <v>2.51</v>
       </c>
       <c r="S3" t="n">
-        <v>1.2965</v>
+        <v>0.4484</v>
       </c>
       <c r="T3" t="n">
-        <v>0.9927</v>
+        <v>0.2687</v>
       </c>
       <c r="U3" t="n">
-        <v>0.3039</v>
+        <v>0.1797</v>
       </c>
       <c r="V3" t="n">
         <v>2.255</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>2.8934</v>
+        <v>3.3112</v>
       </c>
       <c r="E4" t="n">
-        <v>0.4532</v>
+        <v>0.9703000000000001</v>
       </c>
       <c r="F4" t="n">
-        <v>2.4402</v>
+        <v>2.3409</v>
       </c>
       <c r="G4" t="n">
         <v>4.2238</v>
@@ -766,13 +766,13 @@
         <v>2.51</v>
       </c>
       <c r="S4" t="n">
-        <v>0.0445</v>
+        <v>0.4623</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.4691</v>
+        <v>0.048</v>
       </c>
       <c r="U4" t="n">
-        <v>0.5135999999999999</v>
+        <v>0.4143</v>
       </c>
       <c r="V4" t="n">
         <v>0.9421</v>
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>1.6336</v>
+        <v>2.2419</v>
       </c>
       <c r="E5" t="n">
-        <v>0.3746</v>
+        <v>0.6849</v>
       </c>
       <c r="F5" t="n">
-        <v>1.259</v>
+        <v>1.557</v>
       </c>
       <c r="G5" t="n">
         <v>-2.053</v>
@@ -844,13 +844,13 @@
         <v>3.8616</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.1323</v>
+        <v>0.4759</v>
       </c>
       <c r="T5" t="n">
-        <v>0.0547</v>
+        <v>0.365</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.187</v>
+        <v>0.111</v>
       </c>
       <c r="V5" t="n">
         <v>-0.0426</v>
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.9588</v>
+        <v>0.8762</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.9524</v>
+        <v>-1.1592</v>
       </c>
       <c r="F6" t="n">
-        <v>1.9112</v>
+        <v>2.0354</v>
       </c>
       <c r="G6" t="n">
         <v>-0.001</v>
@@ -922,13 +922,13 @@
         <v>0.9654</v>
       </c>
       <c r="S6" t="n">
-        <v>0.3034</v>
+        <v>0.2207</v>
       </c>
       <c r="T6" t="n">
-        <v>0.4963</v>
+        <v>0.2894</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.1929</v>
+        <v>-0.0687</v>
       </c>
       <c r="V6" t="n">
         <v>0.6565</v>
@@ -943,7 +943,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>A. ROMERO GARCIA</t>
+          <t>F. QUERO CARMONA</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>0.2824</v>
+        <v>-0.1448</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.6593</v>
+        <v>-0.0871</v>
       </c>
       <c r="F7" t="n">
-        <v>0.9417</v>
+        <v>-0.0577</v>
       </c>
       <c r="G7" t="n">
-        <v>0.4231</v>
+        <v>1.3673</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.2347</v>
+        <v>1.2136</v>
       </c>
       <c r="I7" t="n">
-        <v>0.6578000000000001</v>
+        <v>0.1537</v>
       </c>
       <c r="J7" t="n">
-        <v>0.6925</v>
+        <v>1.8921</v>
       </c>
       <c r="K7" t="n">
-        <v>0.0414</v>
+        <v>1.076</v>
       </c>
       <c r="L7" t="n">
-        <v>0.6511</v>
+        <v>0.8161</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.2693</v>
+        <v>-0.5248</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.2761</v>
+        <v>0.1376</v>
       </c>
       <c r="O7" t="n">
-        <v>0.0068</v>
+        <v>-0.6624</v>
       </c>
       <c r="P7" t="n">
-        <v>-0.9654</v>
+        <v>0.1931</v>
       </c>
       <c r="Q7" t="n">
         <v>-1.9308</v>
       </c>
       <c r="R7" t="n">
-        <v>0.9654</v>
+        <v>2.1239</v>
       </c>
       <c r="S7" t="n">
-        <v>0.4965</v>
+        <v>0.3793</v>
       </c>
       <c r="T7" t="n">
-        <v>0.579</v>
+        <v>-0.0485</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.0825</v>
+        <v>0.4278</v>
       </c>
       <c r="V7" t="n">
-        <v>0.3282</v>
+        <v>-2.0845</v>
       </c>
       <c r="W7" t="n">
         <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>0.3282</v>
+        <v>-2.0845</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>R. DEUS VERA</t>
+          <t>A. ROMERO GARCIA</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.1299</v>
+        <v>-0.2554</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.3126</v>
+        <v>-1.073</v>
       </c>
       <c r="F8" t="n">
-        <v>0.1826</v>
+        <v>0.8176</v>
       </c>
       <c r="G8" t="n">
-        <v>-1.3682</v>
+        <v>0.4231</v>
       </c>
       <c r="H8" t="n">
-        <v>-1.6824</v>
+        <v>-0.2347</v>
       </c>
       <c r="I8" t="n">
-        <v>0.3142</v>
+        <v>0.6578000000000001</v>
       </c>
       <c r="J8" t="n">
-        <v>-0.2089</v>
+        <v>0.6925</v>
       </c>
       <c r="K8" t="n">
-        <v>-0.3717</v>
+        <v>0.0414</v>
       </c>
       <c r="L8" t="n">
-        <v>0.1628</v>
+        <v>0.6511</v>
       </c>
       <c r="M8" t="n">
-        <v>-1.1593</v>
+        <v>-0.2693</v>
       </c>
       <c r="N8" t="n">
-        <v>-1.3107</v>
+        <v>-0.2761</v>
       </c>
       <c r="O8" t="n">
-        <v>0.1514</v>
+        <v>0.0068</v>
       </c>
       <c r="P8" t="n">
-        <v>-0.3862</v>
+        <v>-0.9654</v>
       </c>
       <c r="Q8" t="n">
         <v>-1.9308</v>
       </c>
       <c r="R8" t="n">
-        <v>1.5446</v>
+        <v>0.9654</v>
       </c>
       <c r="S8" t="n">
-        <v>1.2962</v>
+        <v>-0.0414</v>
       </c>
       <c r="T8" t="n">
-        <v>1.2133</v>
+        <v>0.1653</v>
       </c>
       <c r="U8" t="n">
-        <v>0.0829</v>
+        <v>-0.2067</v>
       </c>
       <c r="V8" t="n">
         <v>0.3282</v>
       </c>
       <c r="W8" t="n">
-        <v>0.6138</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>-0.2856</v>
+        <v>0.3282</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>F. QUERO CARMONA</t>
+          <t>R. DEUS VERA</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1111,73 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.6786</v>
+        <v>-0.8331</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.3974</v>
+        <v>-1.1399</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.2812</v>
+        <v>0.3068</v>
       </c>
       <c r="G9" t="n">
-        <v>1.3673</v>
+        <v>-1.3682</v>
       </c>
       <c r="H9" t="n">
-        <v>1.2136</v>
+        <v>-1.6824</v>
       </c>
       <c r="I9" t="n">
-        <v>0.1537</v>
+        <v>0.3142</v>
       </c>
       <c r="J9" t="n">
-        <v>1.8921</v>
+        <v>-0.2089</v>
       </c>
       <c r="K9" t="n">
-        <v>1.076</v>
+        <v>-0.3717</v>
       </c>
       <c r="L9" t="n">
-        <v>0.8161</v>
+        <v>0.1628</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.5248</v>
+        <v>-1.1593</v>
       </c>
       <c r="N9" t="n">
-        <v>0.1376</v>
+        <v>-1.3107</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.6624</v>
+        <v>0.1514</v>
       </c>
       <c r="P9" t="n">
-        <v>0.1931</v>
+        <v>-0.3862</v>
       </c>
       <c r="Q9" t="n">
         <v>-1.9308</v>
       </c>
       <c r="R9" t="n">
-        <v>2.1239</v>
+        <v>1.5446</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.1545</v>
+        <v>0.593</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.3587</v>
+        <v>0.3859</v>
       </c>
       <c r="U9" t="n">
-        <v>0.2043</v>
+        <v>0.2071</v>
       </c>
       <c r="V9" t="n">
-        <v>-2.0845</v>
+        <v>0.3282</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>0.6138</v>
       </c>
       <c r="X9" t="n">
-        <v>-2.0845</v>
+        <v>-0.2856</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>L. NVE MALEVA</t>
+          <t>A. SOUSA SILVA</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,64 +1189,64 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-1.8654</v>
+        <v>-1.8052</v>
       </c>
       <c r="E10" t="n">
-        <v>-2.7724</v>
+        <v>-1.2635</v>
       </c>
       <c r="F10" t="n">
-        <v>0.9071</v>
+        <v>-0.5417</v>
       </c>
       <c r="G10" t="n">
-        <v>-1.704</v>
+        <v>-0.4359</v>
       </c>
       <c r="H10" t="n">
-        <v>-1.7582</v>
+        <v>0.7239</v>
       </c>
       <c r="I10" t="n">
-        <v>0.0542</v>
+        <v>-1.1598</v>
       </c>
       <c r="J10" t="n">
-        <v>-1.3035</v>
+        <v>0.9031</v>
       </c>
       <c r="K10" t="n">
-        <v>-1.3442</v>
+        <v>0.8624000000000001</v>
       </c>
       <c r="L10" t="n">
         <v>0.0407</v>
       </c>
       <c r="M10" t="n">
-        <v>-0.4005</v>
+        <v>-1.339</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.414</v>
+        <v>-0.1385</v>
       </c>
       <c r="O10" t="n">
-        <v>0.0135</v>
+        <v>-1.2005</v>
       </c>
       <c r="P10" t="n">
-        <v>0.1931</v>
+        <v>-0.9654</v>
       </c>
       <c r="Q10" t="n">
-        <v>-0.9654</v>
+        <v>-2.8962</v>
       </c>
       <c r="R10" t="n">
-        <v>1.1585</v>
+        <v>1.9308</v>
       </c>
       <c r="S10" t="n">
-        <v>1.5723</v>
+        <v>-0.0757</v>
       </c>
       <c r="T10" t="n">
-        <v>0.5238</v>
+        <v>0.1584</v>
       </c>
       <c r="U10" t="n">
-        <v>1.0485</v>
+        <v>-0.234</v>
       </c>
       <c r="V10" t="n">
-        <v>-1.9268</v>
+        <v>-0.3282</v>
       </c>
       <c r="W10" t="n">
-        <v>-1.0273</v>
+        <v>0.5712</v>
       </c>
       <c r="X10" t="n">
         <v>-0.8995</v>
@@ -1255,7 +1255,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>A. SOUSA SILVA</t>
+          <t>L. NVE MALEVA</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,64 +1267,64 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-2.4464</v>
+        <v>-2.3413</v>
       </c>
       <c r="E11" t="n">
-        <v>-1.7806</v>
+        <v>-2.8758</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.6659</v>
+        <v>0.5346</v>
       </c>
       <c r="G11" t="n">
-        <v>-0.4359</v>
+        <v>-1.704</v>
       </c>
       <c r="H11" t="n">
-        <v>0.7239</v>
+        <v>-1.7582</v>
       </c>
       <c r="I11" t="n">
-        <v>-1.1598</v>
+        <v>0.0542</v>
       </c>
       <c r="J11" t="n">
-        <v>0.9031</v>
+        <v>-1.3035</v>
       </c>
       <c r="K11" t="n">
-        <v>0.8624000000000001</v>
+        <v>-1.3442</v>
       </c>
       <c r="L11" t="n">
         <v>0.0407</v>
       </c>
       <c r="M11" t="n">
-        <v>-1.339</v>
+        <v>-0.4005</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.1385</v>
+        <v>-0.414</v>
       </c>
       <c r="O11" t="n">
-        <v>-1.2005</v>
+        <v>0.0135</v>
       </c>
       <c r="P11" t="n">
+        <v>0.1931</v>
+      </c>
+      <c r="Q11" t="n">
         <v>-0.9654</v>
       </c>
-      <c r="Q11" t="n">
-        <v>-2.8962</v>
-      </c>
       <c r="R11" t="n">
-        <v>1.9308</v>
+        <v>1.1585</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.717</v>
+        <v>1.0964</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.3587</v>
+        <v>0.4204</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.3582</v>
+        <v>0.676</v>
       </c>
       <c r="V11" t="n">
-        <v>-0.3282</v>
+        <v>-1.9268</v>
       </c>
       <c r="W11" t="n">
-        <v>0.5712</v>
+        <v>-1.0273</v>
       </c>
       <c r="X11" t="n">
         <v>-0.8995</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>19.6916</v>
+        <v>19.6917</v>
       </c>
       <c r="E12" t="n">
-        <v>8.0808</v>
+        <v>8.081100000000001</v>
       </c>
       <c r="F12" t="n">
-        <v>11.6106</v>
+        <v>11.6109</v>
       </c>
       <c r="G12" t="n">
         <v>10.7242</v>
@@ -1381,7 +1381,7 @@
         <v>-7.9355</v>
       </c>
       <c r="P12" t="n">
-        <v>0.9654000000000003</v>
+        <v>0.9654000000000005</v>
       </c>
       <c r="Q12" t="n">
         <v>-20.2734</v>
@@ -1390,16 +1390,16 @@
         <v>21.2387</v>
       </c>
       <c r="S12" t="n">
-        <v>4.2762</v>
+        <v>4.276200000000001</v>
       </c>
       <c r="T12" t="n">
-        <v>2.0662</v>
+        <v>2.066</v>
       </c>
       <c r="U12" t="n">
         <v>2.2104</v>
       </c>
       <c r="V12" t="n">
-        <v>3.725700000000001</v>
+        <v>3.7257</v>
       </c>
       <c r="W12" t="n">
         <v>5.5544</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>3.3151</v>
+        <v>2.6505</v>
       </c>
       <c r="E13" t="n">
-        <v>3.3815</v>
+        <v>2.5542</v>
       </c>
       <c r="F13" t="n">
-        <v>-0.0664</v>
+        <v>0.0963</v>
       </c>
       <c r="G13" t="n">
         <v>2.1174</v>
@@ -1468,13 +1468,13 @@
         <v>2.1239</v>
       </c>
       <c r="S13" t="n">
-        <v>1.1747</v>
+        <v>0.51</v>
       </c>
       <c r="T13" t="n">
-        <v>1.1579</v>
+        <v>0.3305</v>
       </c>
       <c r="U13" t="n">
-        <v>0.0168</v>
+        <v>0.1795</v>
       </c>
       <c r="V13" t="n">
         <v>0.023</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>-0.292</v>
+        <v>-0.1389</v>
       </c>
       <c r="E14" t="n">
-        <v>0.08890000000000001</v>
+        <v>0.1923</v>
       </c>
       <c r="F14" t="n">
-        <v>-0.3809</v>
+        <v>-0.3312</v>
       </c>
       <c r="G14" t="n">
         <v>-0.5457</v>
@@ -1546,13 +1546,13 @@
         <v>0.1931</v>
       </c>
       <c r="S14" t="n">
-        <v>0.0606</v>
+        <v>0.2137</v>
       </c>
       <c r="T14" t="n">
-        <v>0.0275</v>
+        <v>0.131</v>
       </c>
       <c r="U14" t="n">
-        <v>0.0331</v>
+        <v>0.0828</v>
       </c>
       <c r="V14" t="n">
         <v>0</v>
@@ -1567,7 +1567,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>B. SOW</t>
+          <t>A. DELICADO DOMINGUEZ</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,73 +1579,73 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>-0.4208</v>
+        <v>-0.2729</v>
       </c>
       <c r="E15" t="n">
-        <v>0</v>
+        <v>0.8136</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.4208</v>
+        <v>-1.0866</v>
       </c>
       <c r="G15" t="n">
-        <v>-0.6138</v>
+        <v>3.1974</v>
       </c>
       <c r="H15" t="n">
-        <v>-0.2069</v>
+        <v>1.5448</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.4069</v>
+        <v>1.6526</v>
       </c>
       <c r="J15" t="n">
-        <v>0</v>
+        <v>4.4947</v>
       </c>
       <c r="K15" t="n">
-        <v>0</v>
+        <v>2.5799</v>
       </c>
       <c r="L15" t="n">
-        <v>0</v>
+        <v>1.9148</v>
       </c>
       <c r="M15" t="n">
-        <v>-0.6138</v>
+        <v>-1.2973</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.2069</v>
+        <v>-1.0351</v>
       </c>
       <c r="O15" t="n">
-        <v>-0.4069</v>
+        <v>-0.2623</v>
       </c>
       <c r="P15" t="n">
-        <v>0.1931</v>
+        <v>-1.3515</v>
       </c>
       <c r="Q15" t="n">
-        <v>0</v>
+        <v>-3.0892</v>
       </c>
       <c r="R15" t="n">
-        <v>0.1931</v>
+        <v>1.7377</v>
       </c>
       <c r="S15" t="n">
-        <v>0</v>
+        <v>-0.2346</v>
       </c>
       <c r="T15" t="n">
-        <v>0</v>
+        <v>-0.221</v>
       </c>
       <c r="U15" t="n">
-        <v>0</v>
+        <v>-0.0136</v>
       </c>
       <c r="V15" t="n">
-        <v>0</v>
+        <v>-1.8842</v>
       </c>
       <c r="W15" t="n">
-        <v>0</v>
+        <v>-0.3709</v>
       </c>
       <c r="X15" t="n">
-        <v>0</v>
+        <v>-1.5133</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>P. REYES ZUR</t>
+          <t>B. SOW</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>-0.7837</v>
+        <v>-0.4208</v>
       </c>
       <c r="E16" t="n">
-        <v>0.4223</v>
+        <v>0</v>
       </c>
       <c r="F16" t="n">
-        <v>-1.2059</v>
+        <v>-0.4208</v>
       </c>
       <c r="G16" t="n">
-        <v>-2.0567</v>
+        <v>-0.6138</v>
       </c>
       <c r="H16" t="n">
-        <v>-0.5104</v>
+        <v>-0.2069</v>
       </c>
       <c r="I16" t="n">
-        <v>-1.5463</v>
+        <v>-0.4069</v>
       </c>
       <c r="J16" t="n">
-        <v>0.0541</v>
+        <v>0</v>
       </c>
       <c r="K16" t="n">
-        <v>-0.0273</v>
+        <v>0</v>
       </c>
       <c r="L16" t="n">
-        <v>0.0814</v>
+        <v>0</v>
       </c>
       <c r="M16" t="n">
-        <v>-2.1107</v>
+        <v>-0.6138</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.483</v>
+        <v>-0.2069</v>
       </c>
       <c r="O16" t="n">
-        <v>-1.6277</v>
+        <v>-0.4069</v>
       </c>
       <c r="P16" t="n">
         <v>0.1931</v>
       </c>
       <c r="Q16" t="n">
-        <v>-0.3862</v>
+        <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>0.5792</v>
+        <v>0.1931</v>
       </c>
       <c r="S16" t="n">
-        <v>0.1378</v>
+        <v>0</v>
       </c>
       <c r="T16" t="n">
-        <v>0.4688</v>
+        <v>0</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.3309</v>
+        <v>0</v>
       </c>
       <c r="V16" t="n">
-        <v>0.9421</v>
+        <v>0</v>
       </c>
       <c r="W16" t="n">
-        <v>0.2856</v>
+        <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>0.6565</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A. DELICADO DOMINGUEZ</t>
+          <t>P. REYES ZUR</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,67 +1735,67 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.899</v>
+        <v>-0.625</v>
       </c>
       <c r="E17" t="n">
-        <v>0.4</v>
+        <v>0.3188</v>
       </c>
       <c r="F17" t="n">
-        <v>-1.2989</v>
+        <v>-0.9439</v>
       </c>
       <c r="G17" t="n">
-        <v>3.1974</v>
+        <v>-2.0567</v>
       </c>
       <c r="H17" t="n">
-        <v>1.5448</v>
+        <v>-0.5104</v>
       </c>
       <c r="I17" t="n">
-        <v>1.6526</v>
+        <v>-1.5463</v>
       </c>
       <c r="J17" t="n">
-        <v>4.4947</v>
+        <v>0.0541</v>
       </c>
       <c r="K17" t="n">
-        <v>2.5799</v>
+        <v>-0.0273</v>
       </c>
       <c r="L17" t="n">
-        <v>1.9148</v>
+        <v>0.0814</v>
       </c>
       <c r="M17" t="n">
-        <v>-1.2973</v>
+        <v>-2.1107</v>
       </c>
       <c r="N17" t="n">
-        <v>-1.0351</v>
+        <v>-0.483</v>
       </c>
       <c r="O17" t="n">
-        <v>-0.2623</v>
+        <v>-1.6277</v>
       </c>
       <c r="P17" t="n">
-        <v>-1.3515</v>
+        <v>0.1931</v>
       </c>
       <c r="Q17" t="n">
-        <v>-3.0892</v>
+        <v>-0.3862</v>
       </c>
       <c r="R17" t="n">
-        <v>1.7377</v>
+        <v>0.5792</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.8607</v>
+        <v>0.2965</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.6347</v>
+        <v>0.3653</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.226</v>
+        <v>-0.0689</v>
       </c>
       <c r="V17" t="n">
-        <v>-1.8842</v>
+        <v>0.9421</v>
       </c>
       <c r="W17" t="n">
-        <v>-0.3709</v>
+        <v>0.2856</v>
       </c>
       <c r="X17" t="n">
-        <v>-1.5133</v>
+        <v>0.6565</v>
       </c>
     </row>
     <row r="18">
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-1.2111</v>
+        <v>-0.8015</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.337</v>
+        <v>-0.4405</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.874</v>
+        <v>-0.361</v>
       </c>
       <c r="G18" t="n">
         <v>-1.6205</v>
@@ -1858,13 +1858,13 @@
         <v>1.5446</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.3476</v>
+        <v>0.062</v>
       </c>
       <c r="T18" t="n">
-        <v>0.1377</v>
+        <v>0.0342</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.4852</v>
+        <v>0.0278</v>
       </c>
       <c r="V18" t="n">
         <v>0.3709</v>
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-1.6108</v>
+        <v>-1.5393</v>
       </c>
       <c r="E19" t="n">
-        <v>-2.0977</v>
+        <v>-1.8908</v>
       </c>
       <c r="F19" t="n">
-        <v>0.4868</v>
+        <v>0.3516</v>
       </c>
       <c r="G19" t="n">
         <v>-0.3257</v>
@@ -1936,13 +1936,13 @@
         <v>0.3862</v>
       </c>
       <c r="S19" t="n">
-        <v>0.4526</v>
+        <v>0.5241</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.0552</v>
+        <v>0.1517</v>
       </c>
       <c r="U19" t="n">
-        <v>0.5077</v>
+        <v>0.3725</v>
       </c>
       <c r="V19" t="n">
         <v>0</v>
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-2.1082</v>
+        <v>-1.8517</v>
       </c>
       <c r="E20" t="n">
-        <v>-1.7653</v>
+        <v>-1.5585</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.3429</v>
+        <v>-0.2933</v>
       </c>
       <c r="G20" t="n">
         <v>-1.1588</v>
@@ -2014,13 +2014,13 @@
         <v>0.3862</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.4359</v>
+        <v>-0.1794</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.1932</v>
+        <v>0.0136</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.2427</v>
+        <v>-0.193</v>
       </c>
       <c r="V20" t="n">
         <v>0.06560000000000001</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-2.8418</v>
+        <v>-2.1053</v>
       </c>
       <c r="E21" t="n">
         <v>-1.9908</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.851</v>
+        <v>-0.1145</v>
       </c>
       <c r="G21" t="n">
         <v>-0.4152</v>
@@ -2092,13 +2092,13 @@
         <v>2.8962</v>
       </c>
       <c r="S21" t="n">
-        <v>-1.1642</v>
+        <v>-0.4277</v>
       </c>
       <c r="T21" t="n">
         <v>-0.2763</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.888</v>
+        <v>-0.1515</v>
       </c>
       <c r="V21" t="n">
         <v>-1.8415</v>
@@ -2113,7 +2113,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>B. VIDARTE CANO</t>
+          <t>G. GARRIDO GUERREIRO DE SOUSA</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,73 +2125,73 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-3.1469</v>
+        <v>-3.419</v>
       </c>
       <c r="E22" t="n">
-        <v>-4.2744</v>
+        <v>-1.1433</v>
       </c>
       <c r="F22" t="n">
-        <v>1.1275</v>
+        <v>-2.2757</v>
       </c>
       <c r="G22" t="n">
-        <v>-4.0361</v>
+        <v>-2.8882</v>
       </c>
       <c r="H22" t="n">
-        <v>-3.8756</v>
+        <v>-0.7249</v>
       </c>
       <c r="I22" t="n">
-        <v>-0.1605</v>
+        <v>-2.1634</v>
       </c>
       <c r="J22" t="n">
-        <v>-1.0483</v>
+        <v>0.2995</v>
       </c>
       <c r="K22" t="n">
-        <v>-2.3573</v>
+        <v>0.4486</v>
       </c>
       <c r="L22" t="n">
-        <v>1.309</v>
+        <v>-0.149</v>
       </c>
       <c r="M22" t="n">
-        <v>-2.9878</v>
+        <v>-3.1878</v>
       </c>
       <c r="N22" t="n">
-        <v>-1.5183</v>
+        <v>-1.1734</v>
       </c>
       <c r="O22" t="n">
-        <v>-1.4695</v>
+        <v>-2.0143</v>
       </c>
       <c r="P22" t="n">
-        <v>-0.5792</v>
+        <v>2.3169</v>
       </c>
       <c r="Q22" t="n">
-        <v>-3.8616</v>
+        <v>-1.1585</v>
       </c>
       <c r="R22" t="n">
-        <v>3.2823</v>
+        <v>3.4754</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.1105</v>
+        <v>-0.7862</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.2213</v>
+        <v>-0.8556</v>
       </c>
       <c r="U22" t="n">
-        <v>0.1108</v>
+        <v>0.0694</v>
       </c>
       <c r="V22" t="n">
-        <v>1.5789</v>
+        <v>-2.0615</v>
       </c>
       <c r="W22" t="n">
-        <v>0.8568</v>
+        <v>0.5712</v>
       </c>
       <c r="X22" t="n">
-        <v>0.7221</v>
+        <v>-2.6327</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>G. GARRIDO GUERREIRO DE SOUSA</t>
+          <t>B. VIDARTE CANO</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,67 +2203,67 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-3.3223</v>
+        <v>-3.8778</v>
       </c>
       <c r="E23" t="n">
-        <v>-1.1433</v>
+        <v>-4.8949</v>
       </c>
       <c r="F23" t="n">
-        <v>-2.179</v>
+        <v>1.0171</v>
       </c>
       <c r="G23" t="n">
-        <v>-2.8882</v>
+        <v>-4.0361</v>
       </c>
       <c r="H23" t="n">
-        <v>-0.7249</v>
+        <v>-3.8756</v>
       </c>
       <c r="I23" t="n">
-        <v>-2.1634</v>
+        <v>-0.1605</v>
       </c>
       <c r="J23" t="n">
-        <v>0.2995</v>
+        <v>-1.0483</v>
       </c>
       <c r="K23" t="n">
-        <v>0.4486</v>
+        <v>-2.3573</v>
       </c>
       <c r="L23" t="n">
-        <v>-0.149</v>
+        <v>1.309</v>
       </c>
       <c r="M23" t="n">
-        <v>-3.1878</v>
+        <v>-2.9878</v>
       </c>
       <c r="N23" t="n">
-        <v>-1.1734</v>
+        <v>-1.5183</v>
       </c>
       <c r="O23" t="n">
-        <v>-2.0143</v>
+        <v>-1.4695</v>
       </c>
       <c r="P23" t="n">
-        <v>2.3169</v>
+        <v>-0.5792</v>
       </c>
       <c r="Q23" t="n">
-        <v>-1.1585</v>
+        <v>-3.8616</v>
       </c>
       <c r="R23" t="n">
-        <v>3.4754</v>
+        <v>3.2823</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.6895</v>
+        <v>-0.8414</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.8556</v>
+        <v>-0.8419</v>
       </c>
       <c r="U23" t="n">
-        <v>0.1661</v>
+        <v>0.0004</v>
       </c>
       <c r="V23" t="n">
-        <v>-2.0615</v>
+        <v>1.5789</v>
       </c>
       <c r="W23" t="n">
-        <v>0.5712</v>
+        <v>0.8568</v>
       </c>
       <c r="X23" t="n">
-        <v>-2.6327</v>
+        <v>0.7221</v>
       </c>
     </row>
     <row r="24">
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-6.3703</v>
+        <v>-5.2215</v>
       </c>
       <c r="E24" t="n">
-        <v>-4.0093</v>
+        <v>-3.2853</v>
       </c>
       <c r="F24" t="n">
-        <v>-2.361</v>
+        <v>-1.9362</v>
       </c>
       <c r="G24" t="n">
         <v>-2.3784</v>
@@ -2326,13 +2326,13 @@
         <v>3.4754</v>
       </c>
       <c r="S24" t="n">
-        <v>-2.4936</v>
+        <v>-1.3449</v>
       </c>
       <c r="T24" t="n">
-        <v>-1.7658</v>
+        <v>-1.0419</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.7278</v>
+        <v>-0.303</v>
       </c>
       <c r="V24" t="n">
         <v>-0.9191</v>
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-19.6918</v>
+        <v>-17.6232</v>
       </c>
       <c r="E25" t="n">
-        <v>-11.3251</v>
+        <v>-11.3252</v>
       </c>
       <c r="F25" t="n">
-        <v>-8.3665</v>
+        <v>-6.2982</v>
       </c>
       <c r="G25" t="n">
         <v>-10.7243</v>
@@ -2395,7 +2395,7 @@
         <v>-11.4166</v>
       </c>
       <c r="P25" t="n">
-        <v>-0.9652000000000002</v>
+        <v>-0.9651999999999996</v>
       </c>
       <c r="Q25" t="n">
         <v>-21.2387</v>
@@ -2404,13 +2404,13 @@
         <v>20.2733</v>
       </c>
       <c r="S25" t="n">
-        <v>-4.2763</v>
+        <v>-2.2079</v>
       </c>
       <c r="T25" t="n">
-        <v>-2.2102</v>
+        <v>-2.2104</v>
       </c>
       <c r="U25" t="n">
-        <v>-2.0661</v>
+        <v>0.002400000000000013</v>
       </c>
       <c r="V25" t="n">
         <v>-3.7258</v>
